--- a/05_Figures/F06_prediction/proteins/trajectory/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/trajectory/comp_hypertrophy/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -149,6 +149,9 @@
     <t xml:space="preserve">PPIF@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">PPP1R2@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAD23B@T3</t>
   </si>
   <si>
@@ -158,70 +161,79 @@
     <t xml:space="preserve">ACAT1@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">BDH1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTH1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LNPK@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARS1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHA@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">AK1@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">BDH1@T3</t>
+    <t xml:space="preserve">CD59@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2S3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMAN2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC23A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYO18A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTUB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP2@T2</t>
   </si>
   <si>
     <t xml:space="preserve">BSG@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">CD59@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTH1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LNPK@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NARS1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC23A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2S3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYO18A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTUB1@T3</t>
+    <t xml:space="preserve">MLEC@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL17@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1H1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB@T2</t>
   </si>
   <si>
     <t xml:space="preserve">PPM1A@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">PPP1R2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMAN2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLEC@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1H1@T3</t>
+    <t xml:space="preserve">RPL12@T3</t>
   </si>
   <si>
     <t xml:space="preserve">SUCLG1@T3</t>
@@ -236,150 +248,144 @@
     <t xml:space="preserve">LETM1@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">MB@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">PGP@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL12@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">ARMT1@T1</t>
   </si>
   <si>
     <t xml:space="preserve">CHCHD7@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">TSFM@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM11@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">DHRS7@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">DYNC1LI1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPD1L@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRKRA@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">TSFM@T2</t>
+    <t xml:space="preserve">SEPTIN9@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC16A1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACY1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDOA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN1@T3</t>
   </si>
   <si>
     <t xml:space="preserve">DUSP3@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF2A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN9@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM11@T3</t>
+    <t xml:space="preserve">EIF4A2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAPDH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPT2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHD@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYPLA2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXE@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRG2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPLOC4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCBD1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKM@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A13@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM11@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMX4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TNPO3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USP15@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAD9@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFG3L2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCYL2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDOC@T2</t>
   </si>
   <si>
     <t xml:space="preserve">ALPK3@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">BIN1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1LI1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPD1L@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL17@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC16A1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCHL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USP15@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACY1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDOC@T2</t>
+    <t xml:space="preserve">ARF4@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5MF@T3</t>
   </si>
   <si>
     <t xml:space="preserve">ATP6V1H@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF4A2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAPDH@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHD@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYPLA2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAXE@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDRG2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPLOC4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCBD1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKM@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A13@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM11@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMX4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAD9@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFG3L2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCYL2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH3A2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDOA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF4@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5MF@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">BDH2@T3</t>
   </si>
   <si>
@@ -413,9 +419,6 @@
     <t xml:space="preserve">COA6@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">COMT@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">CPNE3@T3</t>
   </si>
   <si>
@@ -449,7 +452,7 @@
     <t xml:space="preserve">FABP3@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">FAM98B@T3</t>
+    <t xml:space="preserve">FBLN5@T3</t>
   </si>
   <si>
     <t xml:space="preserve">FITM2@T3</t>
@@ -479,7 +482,7 @@
     <t xml:space="preserve">IDI1@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">JPT2@T2</t>
+    <t xml:space="preserve">IDI1@T3</t>
   </si>
   <si>
     <t xml:space="preserve">KARS1@T1</t>
@@ -503,9 +506,6 @@
     <t xml:space="preserve">MAP4@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">MAPRE3@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">MBNL1@T3</t>
   </si>
   <si>
@@ -566,6 +566,9 @@
     <t xml:space="preserve">POLDIP2@T2</t>
   </si>
   <si>
+    <t xml:space="preserve">PPID@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPP2R2A@T2</t>
   </si>
   <si>
@@ -602,10 +605,7 @@
     <t xml:space="preserve">SCFD1@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">SDHA@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC24C@T3</t>
+    <t xml:space="preserve">SLC44A2@T2</t>
   </si>
   <si>
     <t xml:space="preserve">SOD1@T2</t>
@@ -617,34 +617,16 @@
     <t xml:space="preserve">SPTAN1@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">SRSF2@T1</t>
-  </si>
-  <si>
     <t xml:space="preserve">STAT5B@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">STX7@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">SUB1@T3</t>
   </si>
   <si>
     <t xml:space="preserve">TCAP@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">TKFC@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">TMX1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMX3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TNPO3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOLLIP@T1</t>
   </si>
   <si>
     <t xml:space="preserve">TRIM72@T1</t>
@@ -1049,16 +1031,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.416912885433687</v>
+        <v>-0.49587064189618</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.283516483516484</v>
+        <v>-0.349450549450549</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1082,29 +1064,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.416912885433687</v>
+        <v>-0.49587064189618</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.283516483516484</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.3681592039801</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.527363184079602</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.688785393788258</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.688391074551824</v>
-      </c>
+        <v>-0.349450549450549</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1128,2206 +1102,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.314391615803727</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.204769661238648</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.00371631165746678</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.740803258142909</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.672592587644794</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.260843972971275</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.89205424934215</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.000800132189432645</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.07369684863181</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.25361593113466</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.762975889094282</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.935472639692533</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.14970473981401</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-1.48622614661096</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.0492796327291509</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.320399915270388</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.455591923514362</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-2.52073477687743</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.416312126589344</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.32032252842835</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.537001323897528</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.815292027814309</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.1385725766931</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.435866803081208</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.755819949733604</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.532101349658982</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.0482523446824663</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.348781684681388</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-1.5746018219447</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.25674372772895</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.949327138553212</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.56897655254451</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.12115897655892</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-2.73333683885256</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.418472036880933</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.528826573403288</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.35736219633744</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.703241732909489</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.786986931997439</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.144713346187415</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-2.10842659206563</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.413162100526846</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.517228840021356</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.708124975504165</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.41936425103334</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-1.62236065167538</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.231128289439877</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-1.11182540452099</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.0829634073165784</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.369874489092568</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.919165980398667</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.74802316184</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.469817252697123</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.237916486489652</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.606799608848312</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.164083036489069</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.20036122192404</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.129532183145247</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.1062376072112</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.47791740137733</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.900527996313622</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-1.35485500608139</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.321881448629854</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.583972886884063</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-1.45406124266758</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.515595813804472</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-1.36339898200431</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.541049046885456</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.0774597929257044</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.945816697970784</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.47308411674438</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.63095006882478</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.533351600303718</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.304106476545299</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.207841418776806</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.563669933641974</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-1.88809244223174</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.451894912646477</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.510753742208286</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.447174414516769</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.835494707908311</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.366108227514779</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-1.31665258918123</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.620416338769147</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0.298337174454139</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-1.32674309666899</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.971327730478097</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.367555595480313</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.561379668962897</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.985866754006568</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.704907321411474</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-1.09059438940243</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.568668325742087</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.868478550088008</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.582472693827741</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-2.32126703319527</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.178391351147461</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.120231168888535</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.132167248273804</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0.0526127759912695</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.67332840241517</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.584341620721479</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.403230450705296</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.277011553348258</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.349693334356555</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.50709880506647</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.546016836145455</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.152043510777787</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.322749085608768</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>0.369463712469187</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-1.31968048612389</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.183342592413104</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.75235672157669</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.031051977817349</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>0.0184231340378334</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.01414847294519</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-1.06582155861031</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-1.76532280234943</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-2.29738534371216</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.272764485216614</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.549880542563632</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.19483999534845</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.395722509710907</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.183867105996029</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.37473171680238</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-1.37862561719283</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.426089266945638</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.350149151120929</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.581077614486345</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.46733386102623</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>0.711318022211378</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.667545314520394</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-1.3164880614907</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.218401164441706</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-1.39689078862675</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-1.33892650790508</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.692022522942945</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0.0823747937688681</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-1.25141370071434</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.0618925888531412</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0.164787857718577</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.569038890043442</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.75145574351844</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>0.565108083008904</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.04806595833746</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.873055405974017</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.36346228720923</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.432599960275138</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>0.0627149924243494</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.597697715613657</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.690976778913559</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.935208409760007</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.570912591509664</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.801118735003361</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-2.14903293936661</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.6715041693216</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-1.22713321005718</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.196638036001862</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.306615910660741</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-1.19027323963228</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0.333271801213821</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.019493458976716</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>0.053391238215511</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.727680591521016</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.658047188859835</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.28741032790434</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>0.0514767473711045</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.313277811851543</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.923044743659917</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-1.46347672429936</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.680585624651066</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-1.66688129795287</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-3.82389991784017</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-1.0563001188226</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>0.165091015288303</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.918788442772176</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-2.0188020237519</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.99478601364969</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.248153751988245</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.39284641546642</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.176026865207156</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.38969748802905</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.194497678896362</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.319943043459799</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.426408872089876</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-1.42511214082101</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-1.1071650367265</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.350298411557094</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.0974917990960125</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.468256400678709</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.521504387651416</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.26267504329276</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.58138252057327</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.314784841229863</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.0667553129690721</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.33700572896378</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>0.106656046688726</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-1.47111666444335</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.13938537900948</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.525031693494257</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3370,7 +1144,7 @@
         <v>9.43</v>
       </c>
       <c r="E2" t="n">
-        <v>4.80173312983308</v>
+        <v>4.60395042664854</v>
       </c>
     </row>
     <row r="3">
@@ -3387,7 +1161,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0950939607707038</v>
+        <v>-0.491831238400351</v>
       </c>
     </row>
     <row r="4">
@@ -3404,7 +1178,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.787752577936553</v>
+        <v>-0.819118884438827</v>
       </c>
     </row>
     <row r="5">
@@ -3421,7 +1195,7 @@
         <v>10.45</v>
       </c>
       <c r="E5" t="n">
-        <v>0.212266810670676</v>
+        <v>0.430056651451254</v>
       </c>
     </row>
     <row r="6">
@@ -3438,7 +1212,7 @@
         <v>14.93</v>
       </c>
       <c r="E6" t="n">
-        <v>4.12817241862306</v>
+        <v>1.66647480050717</v>
       </c>
     </row>
     <row r="7">
@@ -3455,7 +1229,7 @@
         <v>13.79</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0845175310374437</v>
+        <v>-0.143729934667308</v>
       </c>
     </row>
     <row r="8">
@@ -3472,7 +1246,7 @@
         <v>0.79</v>
       </c>
       <c r="E8" t="n">
-        <v>4.15010062509643</v>
+        <v>4.35065741836483</v>
       </c>
     </row>
     <row r="9">
@@ -3489,7 +1263,7 @@
         <v>0.85</v>
       </c>
       <c r="E9" t="n">
-        <v>4.44606432766847</v>
+        <v>6.16797685581475</v>
       </c>
     </row>
     <row r="10">
@@ -3506,7 +1280,7 @@
         <v>-4.09</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.501058211122552</v>
+        <v>-0.639375394314838</v>
       </c>
     </row>
     <row r="11">
@@ -3523,7 +1297,7 @@
         <v>-0.74</v>
       </c>
       <c r="E11" t="n">
-        <v>0.83070972139337</v>
+        <v>1.01635934362025</v>
       </c>
     </row>
     <row r="12">
@@ -3540,7 +1314,7 @@
         <v>-1.86</v>
       </c>
       <c r="E12" t="n">
-        <v>9.02677274797049</v>
+        <v>8.70313104018357</v>
       </c>
     </row>
     <row r="13">
@@ -3557,7 +1331,7 @@
         <v>-6.6</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3307173387507</v>
+        <v>1.67830589861671</v>
       </c>
     </row>
     <row r="14">
@@ -3574,7 +1348,7 @@
         <v>-5.99</v>
       </c>
       <c r="E14" t="n">
-        <v>6.16759171712491</v>
+        <v>6.20289457963375</v>
       </c>
     </row>
     <row r="15">
@@ -3591,7 +1365,7 @@
         <v>-0.48</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.84702703852324</v>
+        <v>-0.971610327531814</v>
       </c>
     </row>
   </sheetData>
@@ -3786,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -3905,10 +1679,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="19">
@@ -3922,10 +1696,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="20">
@@ -3939,10 +1713,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="21">
@@ -4007,10 +1781,10 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="25">
@@ -4024,10 +1798,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="26">
@@ -4041,10 +1815,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="27">
@@ -4058,10 +1832,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="28">
@@ -4075,10 +1849,10 @@
         <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.714285714285714</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="29">
@@ -4092,10 +1866,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="30">
@@ -4109,10 +1883,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="31">
@@ -4126,10 +1900,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="32">
@@ -4177,10 +1951,10 @@
         <v>69</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
@@ -4262,10 +2036,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="40">
@@ -4279,10 +2053,10 @@
         <v>75</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="41">
@@ -4330,10 +2104,10 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="44">
@@ -4398,10 +2172,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="48">
@@ -4415,10 +2189,10 @@
         <v>83</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="49">
@@ -4432,10 +2206,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="50">
@@ -4500,10 +2274,10 @@
         <v>88</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="54">
@@ -4517,10 +2291,10 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="55">
@@ -4534,10 +2308,10 @@
         <v>90</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="56">
@@ -4551,10 +2325,10 @@
         <v>91</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="57">
@@ -4568,10 +2342,10 @@
         <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="58">
@@ -4585,10 +2359,10 @@
         <v>93</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="59">
@@ -4602,10 +2376,10 @@
         <v>94</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="60">
@@ -4925,10 +2699,10 @@
         <v>113</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="79">
@@ -6560,108 +4334,6 @@
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="s">
-        <v>210</v>
-      </c>
-      <c r="D175" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="s">
-        <v>211</v>
-      </c>
-      <c r="D176" t="n">
-        <v>1</v>
-      </c>
-      <c r="E176" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="s">
-        <v>212</v>
-      </c>
-      <c r="D177" t="n">
-        <v>1</v>
-      </c>
-      <c r="E177" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="s">
-        <v>213</v>
-      </c>
-      <c r="D178" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="s">
-        <v>214</v>
-      </c>
-      <c r="D179" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="s">
-        <v>215</v>
-      </c>
-      <c r="D180" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/trajectory/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/trajectory/comp_hypertrophy/spls/c_data/results.xlsx
@@ -1067,7 +1067,7 @@
         <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.49587064189618</v>
@@ -1075,10 +1075,18 @@
       <c r="I3" t="n">
         <v>-0.349450549450549</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.422885572139304</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.641791044776119</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.697884431372748</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.726463436733434</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1102,6 +1110,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.178386371183502</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.534780951169682</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.0112375872815891</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.757036598580952</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.747670593401199</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.387005769943128</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.85753674830958</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0184061255434173</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.13522127220932</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.4112022044471</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.947855144031871</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.887102228716325</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.17136330248189</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.33481067092936</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0184916633623144</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.37550909833666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.507891190434642</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-2.74977413953894</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.441016125681406</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.60946967896246</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.596807694016784</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.861766421873225</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.971133720033034</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.252478758737649</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.94862344697988</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.746445873535204</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.018282508220959</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.000424598970729995</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.48302877001622</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.32715272107088</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.841139244570915</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.5252624494955</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.1456525906354</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-2.78122756342719</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.517658009884922</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.477765839509608</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.37681695900029</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.376774252186877</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.694744120811325</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.553198381663211</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-2.88984391014458</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.0839778245951441</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.420400454916812</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.654518801938852</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.32661688383351</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.43445822214679</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.190638372563972</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.798841535639753</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.0683614205114842</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.229178938532759</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.29451022503158</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.570282531163137</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.210188135579164</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.140765828524909</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.653436563335696</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.108368124703729</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.981534892669096</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.161308146527117</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.04262374715781</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.363216336959066</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.692001907786346</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1.28418005102046</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.333687186760373</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.381127107408338</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.87425468020271</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.582797576130476</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-1.50648477210045</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.346243247872453</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.482972090586949</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.01641630608427</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.44526844093906</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.6909981464937</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.467155934588614</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.292899721510488</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.217628851231764</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.496076500186172</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.73510058881832</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.493637219039065</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.578247659520637</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.435700984217113</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.576115323653967</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.390473438166304</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.27952992219636</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.653994147594193</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.0659159847553286</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-1.32735397036357</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.43011810895472</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.320568451429213</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.601921634045507</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.860187351500588</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.530110889596353</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.23451756121722</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.545735797009584</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.05725458981113</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.491003361534893</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-1.6082252461423</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.127889894375107</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.193776600975321</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.30988294419865</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.095634382611361</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.703487109101467</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.630904792797886</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.307904859902137</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.257629044534201</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.584283991701713</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.91746204014987</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.633151891167088</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.0590763157224261</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.202297183349787</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.336044724847555</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-1.13237069772878</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.230339997310217</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1.20601948008485</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.00554867111888202</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.0161035294661616</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.905139038267932</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.553484409942278</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-2.84847268502238</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-2.30845488081457</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.306871553942654</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.578004086375791</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.336203194547442</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.570405300861034</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.0131731733912006</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.04587274480671</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.53734732596498</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.459757009056941</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.400954520995765</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.78457150586949</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.36203143085912</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.700394817847745</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.91151793069739</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.37513290991871</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.22821524975816</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-1.39385996187801</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-1.51382814789949</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.612040208773655</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.134542903132038</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.09800627930271</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.0401779975752106</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.173569048734062</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.294782427587516</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-2.2424287092721</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.520857104074849</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.890673833182398</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.800471998554451</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.47560569321183</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.536989376274883</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.104098103643881</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.641639133327358</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.778948507505609</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.884731305979883</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.496939894587486</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.645682921148561</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.74912364985047</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.623131110446761</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.19078958913604</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.249935340046409</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.225835852573003</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.60660690836099</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.22785293272274</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.0825159108319804</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.018805732876227</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-1.65224477329181</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.607713706402654</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.26707788642786</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.134178607087164</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.310476205039419</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.997149461064794</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.25035278547808</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.580968315800633</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.61534446038333</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-4.10729220043018</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-1.21134999652218</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.173018619721536</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1.01004095072509</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-2.08752034063679</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.987291379888131</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.168077013612831</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.331558829431681</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.072367412724321</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.55604542205232</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.28943210827659</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.319840946387087</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.365386233091289</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.28342456652318</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.17184024905534</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.377172134524943</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.0728824366303257</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.438976172565445</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.51775242139589</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1.57377599225851</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.462013067340169</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.368533256317775</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.00423862173578349</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.18156437187097</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.107603296023762</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.36011895141999</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.18315623672065</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.556671737476868</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
